--- a/tables/B【壁纸表】Wallpaper.xlsx
+++ b/tables/B【壁纸表】Wallpaper.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="59">
   <si>
     <t>种类</t>
   </si>
@@ -54,6 +54,12 @@
     <t>筛选</t>
   </si>
   <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>索引</t>
+  </si>
+  <si>
     <t>表头</t>
   </si>
   <si>
@@ -75,6 +81,12 @@
     <t>Video1</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>index1</t>
+  </si>
+  <si>
     <t>持续播放时长</t>
   </si>
   <si>
@@ -88,6 +100,9 @@
   </si>
   <si>
     <t>Video2</t>
+  </si>
+  <si>
+    <t>group2</t>
   </si>
   <si>
     <t>Time2</t>
@@ -202,7 +217,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,12 +234,6 @@
     <font>
       <sz val="9"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -736,133 +745,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -898,7 +907,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1235,19 +1244,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="4" width="22.375" customWidth="1"/>
     <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="3.25" customWidth="1"/>
-    <col min="8" max="8" width="5.125" customWidth="1"/>
+    <col min="7" max="7" width="6.375" customWidth="1"/>
+    <col min="8" max="8" width="8.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:8">
+    <row r="1" s="8" customFormat="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1272,158 +1281,182 @@
       <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="8" customFormat="1" spans="1:8">
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" spans="1:10">
       <c r="A2" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:10">
+      <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="8" customFormat="1" spans="1:8">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="8" customFormat="1" spans="1:10">
+      <c r="A8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:10">
       <c r="A9" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" s="9" customFormat="1" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:10">
       <c r="A10" s="11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11">
@@ -1431,21 +1464,21 @@
       </c>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" s="9" customFormat="1" spans="1:8">
+    <row r="11" s="9" customFormat="1" spans="1:10">
       <c r="A11" s="11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11">
@@ -1453,21 +1486,21 @@
       </c>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" s="9" customFormat="1" spans="1:8">
+    <row r="12" s="9" customFormat="1" spans="1:10">
       <c r="A12" s="11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11">
@@ -1475,21 +1508,21 @@
       </c>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" s="9" customFormat="1" spans="1:8">
+    <row r="13" s="9" customFormat="1" spans="1:10">
       <c r="A13" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11">
@@ -1497,21 +1530,21 @@
       </c>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" s="9" customFormat="1" spans="1:8">
+    <row r="14" s="9" customFormat="1" spans="1:10">
       <c r="A14" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11">
@@ -1519,58 +1552,58 @@
       </c>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" s="9" customFormat="1" spans="1:8">
+    <row r="15" s="9" customFormat="1" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" s="9" customFormat="1" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" s="9" customFormat="1" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" s="9" customFormat="1" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1602,37 +1635,37 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G1"/>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1"/>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1640,24 +1673,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C2" t="str">
         <f>"UI\BGs\"&amp;B2&amp;".jpeg"</f>
         <v>UI\BGs\Wallpaper_001.jpeg</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E2" t="str">
         <f>"Video\Wallpaper\"&amp;D2&amp;".4pm"</f>
         <v>Video\Wallpaper\Wallpaper_001_1.4pm</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H2" t="str">
         <f t="shared" ref="H2:H8" si="0">"Video\Wallpaper\"&amp;G2&amp;".4pm"</f>
@@ -1675,24 +1708,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C3" t="str">
         <f>"UI\BGs\"&amp;B3&amp;".jpeg"</f>
         <v>UI\BGs\LoginBG.jpeg</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E3" t="str">
         <f>"Video\Wallpaper\"&amp;D3&amp;".4pm"</f>
         <v>Video\Wallpaper\Ef_UI_Login_In.4pm</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="0"/>
@@ -1727,7 +1760,7 @@
         <v>Video\Wallpaper\201_show.4pm</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="str">
         <f>A4&amp;"_loop"</f>
@@ -1767,7 +1800,7 @@
         <v>Video\Wallpaper\202_show.4pm</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="str">
         <f>A5&amp;"_loop"</f>
@@ -1807,7 +1840,7 @@
         <v>Video\Wallpaper\203_show.4pm</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="str">
         <f>A6&amp;"_loop"</f>
@@ -1846,7 +1879,7 @@
         <v>Video\Wallpaper\204_show.4pm</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6" t="str">
         <f>A7&amp;"_loop"</f>
@@ -1885,7 +1918,7 @@
         <v>Video\Wallpaper\205_show.4pm</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="str">
         <f t="shared" ref="G8:G34" si="5">A8&amp;"_loop"</f>
@@ -1924,7 +1957,7 @@
         <v>Video\Wallpaper\206_show.4pm</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="str">
         <f t="shared" si="5"/>
@@ -1963,7 +1996,7 @@
         <v>Video\Wallpaper\207_show.4pm</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2002,7 +2035,7 @@
         <v>Video\Wallpaper\208_show.4pm</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2041,7 +2074,7 @@
         <v>Video\Wallpaper\209_show.4pm</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2080,7 +2113,7 @@
         <v>Video\Wallpaper\210_show.4pm</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2119,7 +2152,7 @@
         <v>Video\Wallpaper\211_show.4pm</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2158,7 +2191,7 @@
         <v>Video\Wallpaper\212_show.4pm</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2197,7 +2230,7 @@
         <v>Video\Wallpaper\301_show.4pm</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2236,7 +2269,7 @@
         <v>Video\Wallpaper\302_show.4pm</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2275,7 +2308,7 @@
         <v>Video\Wallpaper\303_show.4pm</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2314,7 +2347,7 @@
         <v>Video\Wallpaper\304_show.4pm</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2353,7 +2386,7 @@
         <v>Video\Wallpaper\305_show.4pm</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2392,7 +2425,7 @@
         <v>Video\Wallpaper\306_show.4pm</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="6" t="str">
         <f t="shared" si="5"/>
@@ -2431,7 +2464,7 @@
         <v>Video\Wallpaper\401_show.4pm</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="6" t="str">
         <f t="shared" si="5"/>

--- a/tables/B【壁纸表】Wallpaper.xlsx
+++ b/tables/B【壁纸表】Wallpaper.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowHeight="17055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="@Type" sheetId="3" r:id="rId1"/>
@@ -1682,9 +1682,8 @@
       <c r="D2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E2" t="str">
-        <f>"Video\Wallpaper\"&amp;D2&amp;".4pm"</f>
-        <v>Video\Wallpaper\Wallpaper_001_1.4pm</v>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1717,9 +1716,8 @@
       <c r="D3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E3" t="str">
-        <f>"Video\Wallpaper\"&amp;D3&amp;".4pm"</f>
-        <v>Video\Wallpaper\Ef_UI_Login_In.4pm</v>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
